--- a/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -709,13 +709,13 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1836300</v>
+        <v>1836700</v>
       </c>
       <c r="E8" s="3">
-        <v>887200</v>
+        <v>887400</v>
       </c>
       <c r="F8" s="3">
-        <v>966700</v>
+        <v>966900</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>3</v>
@@ -736,13 +736,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1410200</v>
+        <v>1410500</v>
       </c>
       <c r="E9" s="3">
-        <v>854100</v>
+        <v>854200</v>
       </c>
       <c r="F9" s="3">
-        <v>988200</v>
+        <v>988400</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>3</v>
@@ -921,13 +921,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1749300</v>
+        <v>1749600</v>
       </c>
       <c r="E17" s="3">
-        <v>1011500</v>
+        <v>1011700</v>
       </c>
       <c r="F17" s="3">
-        <v>1291200</v>
+        <v>1291500</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>3</v>
@@ -948,10 +948,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>87000</v>
+        <v>87100</v>
       </c>
       <c r="E18" s="3">
-        <v>-124200</v>
+        <v>-124300</v>
       </c>
       <c r="F18" s="3">
         <v>-324600</v>
@@ -1015,13 +1015,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>303800</v>
+        <v>302900</v>
       </c>
       <c r="E21" s="3">
-        <v>60600</v>
+        <v>59800</v>
       </c>
       <c r="F21" s="3">
-        <v>-150500</v>
+        <v>-151400</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
@@ -1069,13 +1069,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-73000</v>
+        <v>-73100</v>
       </c>
       <c r="E23" s="3">
         <v>-245000</v>
       </c>
       <c r="F23" s="3">
-        <v>-456200</v>
+        <v>-456300</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>3</v>
@@ -1153,10 +1153,10 @@
         <v>-142500</v>
       </c>
       <c r="E26" s="3">
-        <v>-224300</v>
+        <v>-224400</v>
       </c>
       <c r="F26" s="3">
-        <v>-504100</v>
+        <v>-504200</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>3</v>
@@ -1183,7 +1183,7 @@
         <v>-202100</v>
       </c>
       <c r="F27" s="3">
-        <v>-483200</v>
+        <v>-483300</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1345,7 +1345,7 @@
         <v>-202100</v>
       </c>
       <c r="F33" s="3">
-        <v>-483200</v>
+        <v>-483300</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1399,7 +1399,7 @@
         <v>-202100</v>
       </c>
       <c r="F35" s="3">
-        <v>-483200</v>
+        <v>-483300</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -1478,13 +1478,13 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>542800</v>
+        <v>542900</v>
       </c>
       <c r="E41" s="3">
-        <v>956000</v>
+        <v>956200</v>
       </c>
       <c r="F41" s="3">
-        <v>521600</v>
+        <v>521700</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>3</v>
@@ -1559,7 +1559,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>32100</v>
+        <v>32200</v>
       </c>
       <c r="E44" s="3">
         <v>27000</v>
@@ -1613,13 +1613,13 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>810500</v>
+        <v>810700</v>
       </c>
       <c r="E46" s="3">
-        <v>1179500</v>
+        <v>1179700</v>
       </c>
       <c r="F46" s="3">
-        <v>846200</v>
+        <v>846400</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>3</v>
@@ -1640,10 +1640,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>554100</v>
+        <v>554200</v>
       </c>
       <c r="E47" s="3">
-        <v>414900</v>
+        <v>415000</v>
       </c>
       <c r="F47" s="3">
         <v>278400</v>
@@ -1667,13 +1667,13 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3861700</v>
+        <v>3862400</v>
       </c>
       <c r="E48" s="3">
-        <v>3990300</v>
+        <v>3991100</v>
       </c>
       <c r="F48" s="3">
-        <v>3993300</v>
+        <v>3994000</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
@@ -1694,13 +1694,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>871600</v>
+        <v>871800</v>
       </c>
       <c r="E49" s="3">
-        <v>892900</v>
+        <v>893100</v>
       </c>
       <c r="F49" s="3">
-        <v>906700</v>
+        <v>906800</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -1829,13 +1829,13 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6111300</v>
+        <v>6112400</v>
       </c>
       <c r="E54" s="3">
-        <v>6491100</v>
+        <v>6492300</v>
       </c>
       <c r="F54" s="3">
-        <v>6037900</v>
+        <v>6039000</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>3</v>
@@ -1936,7 +1936,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>480500</v>
+        <v>480600</v>
       </c>
       <c r="E59" s="3">
         <v>443500</v>
@@ -1963,13 +1963,13 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800100</v>
+        <v>800200</v>
       </c>
       <c r="E60" s="3">
-        <v>650200</v>
+        <v>650300</v>
       </c>
       <c r="F60" s="3">
-        <v>635600</v>
+        <v>635700</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>3</v>
@@ -1990,13 +1990,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2545600</v>
+        <v>2546100</v>
       </c>
       <c r="E61" s="3">
-        <v>2838200</v>
+        <v>2838700</v>
       </c>
       <c r="F61" s="3">
-        <v>2086500</v>
+        <v>2086900</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3414200</v>
+        <v>3414800</v>
       </c>
       <c r="E66" s="3">
-        <v>3548900</v>
+        <v>3549600</v>
       </c>
       <c r="F66" s="3">
-        <v>2855000</v>
+        <v>2855500</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>3</v>
@@ -2273,13 +2273,13 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2124000</v>
+        <v>2124400</v>
       </c>
       <c r="E72" s="3">
-        <v>2416900</v>
+        <v>2417400</v>
       </c>
       <c r="F72" s="3">
-        <v>2717000</v>
+        <v>2717600</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
@@ -2381,13 +2381,13 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2697100</v>
+        <v>2697600</v>
       </c>
       <c r="E76" s="3">
-        <v>2942200</v>
+        <v>2942700</v>
       </c>
       <c r="F76" s="3">
-        <v>3182900</v>
+        <v>3183500</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>3</v>
@@ -2473,7 +2473,7 @@
         <v>-202100</v>
       </c>
       <c r="F81" s="3">
-        <v>-483200</v>
+        <v>-483300</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
@@ -2507,10 +2507,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>264400</v>
+        <v>264500</v>
       </c>
       <c r="E83" s="3">
-        <v>236100</v>
+        <v>236200</v>
       </c>
       <c r="F83" s="3">
         <v>238800</v>
@@ -2669,10 +2669,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>504400</v>
+        <v>504500</v>
       </c>
       <c r="E89" s="3">
-        <v>100500</v>
+        <v>100600</v>
       </c>
       <c r="F89" s="3">
         <v>-102700</v>
@@ -2790,13 +2790,13 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-241900</v>
+        <v>-242000</v>
       </c>
       <c r="E94" s="3">
         <v>-128200</v>
       </c>
       <c r="F94" s="3">
-        <v>-273400</v>
+        <v>-273500</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>3</v>
@@ -2938,13 +2938,13 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-611000</v>
+        <v>-611100</v>
       </c>
       <c r="E100" s="3">
-        <v>486400</v>
+        <v>486500</v>
       </c>
       <c r="F100" s="3">
-        <v>-479300</v>
+        <v>-479400</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
@@ -2992,13 +2992,13 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-340900</v>
+        <v>-341000</v>
       </c>
       <c r="E102" s="3">
-        <v>467000</v>
+        <v>467100</v>
       </c>
       <c r="F102" s="3">
-        <v>-858800</v>
+        <v>-859000</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>GMALY</t>
   </si>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -702,23 +702,26 @@
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1836700</v>
+        <v>2161100</v>
       </c>
       <c r="E8" s="3">
-        <v>887400</v>
+        <v>1824600</v>
       </c>
       <c r="F8" s="3">
-        <v>966900</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+        <v>881600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>960500</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -729,23 +732,26 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1410500</v>
+        <v>1617300</v>
       </c>
       <c r="E9" s="3">
-        <v>854200</v>
+        <v>1401300</v>
       </c>
       <c r="F9" s="3">
-        <v>988400</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>848600</v>
+      </c>
+      <c r="G9" s="3">
+        <v>981900</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -756,23 +762,26 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>426100</v>
+        <v>543800</v>
       </c>
       <c r="E10" s="3">
-        <v>33200</v>
+        <v>423400</v>
       </c>
       <c r="F10" s="3">
-        <v>-21600</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+        <v>33000</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-21400</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -783,9 +792,12 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -797,8 +809,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -823,9 +836,12 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -850,23 +866,26 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>77900</v>
+        <v>6300</v>
       </c>
       <c r="E14" s="3">
-        <v>48800</v>
+        <v>77400</v>
       </c>
       <c r="F14" s="3">
-        <v>126100</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+        <v>48500</v>
+      </c>
+      <c r="G14" s="3">
+        <v>125300</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -877,9 +896,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -904,9 +926,12 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -915,22 +940,23 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1749600</v>
+        <v>1836700</v>
       </c>
       <c r="E17" s="3">
-        <v>1011700</v>
+        <v>1738100</v>
       </c>
       <c r="F17" s="3">
-        <v>1291500</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
+        <v>1005100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1283000</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -941,23 +967,26 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>87100</v>
+        <v>324400</v>
       </c>
       <c r="E18" s="3">
-        <v>-124300</v>
+        <v>86500</v>
       </c>
       <c r="F18" s="3">
-        <v>-324600</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>-123500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-322500</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -968,9 +997,12 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -982,22 +1014,23 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-48500</v>
+        <v>-54300</v>
       </c>
       <c r="E20" s="3">
-        <v>-52000</v>
+        <v>-48200</v>
       </c>
       <c r="F20" s="3">
-        <v>-65500</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+        <v>-51700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-65100</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1008,23 +1041,26 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>302900</v>
+        <v>533300</v>
       </c>
       <c r="E21" s="3">
-        <v>59800</v>
+        <v>301000</v>
       </c>
       <c r="F21" s="3">
-        <v>-151400</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>59400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-150400</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1035,23 +1071,26 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>111600</v>
+        <v>127100</v>
       </c>
       <c r="E22" s="3">
-        <v>68700</v>
+        <v>110900</v>
       </c>
       <c r="F22" s="3">
-        <v>66200</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+        <v>68300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>65800</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1062,23 +1101,26 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-73100</v>
+        <v>143000</v>
       </c>
       <c r="E23" s="3">
-        <v>-245000</v>
+        <v>-72600</v>
       </c>
       <c r="F23" s="3">
-        <v>-456300</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+        <v>-243400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-453300</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1089,23 +1131,26 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>69400</v>
+        <v>66400</v>
       </c>
       <c r="E24" s="3">
-        <v>-20600</v>
+        <v>69000</v>
       </c>
       <c r="F24" s="3">
-        <v>47800</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+        <v>-20500</v>
+      </c>
+      <c r="G24" s="3">
+        <v>47500</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1116,9 +1161,12 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1143,23 +1191,26 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-142500</v>
+        <v>76500</v>
       </c>
       <c r="E26" s="3">
-        <v>-224400</v>
+        <v>-141500</v>
       </c>
       <c r="F26" s="3">
-        <v>-504200</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+        <v>-222900</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-500900</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1170,23 +1221,26 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-111000</v>
+        <v>92600</v>
       </c>
       <c r="E27" s="3">
-        <v>-202100</v>
+        <v>-110300</v>
       </c>
       <c r="F27" s="3">
-        <v>-483300</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+        <v>-200800</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-480100</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1197,9 +1251,12 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1224,9 +1281,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,9 +1311,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1278,9 +1341,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1305,23 +1371,26 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>48500</v>
+        <v>54300</v>
       </c>
       <c r="E32" s="3">
-        <v>52000</v>
+        <v>48200</v>
       </c>
       <c r="F32" s="3">
-        <v>65500</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+        <v>51700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>65100</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1332,23 +1401,26 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-111000</v>
+        <v>92600</v>
       </c>
       <c r="E33" s="3">
-        <v>-202100</v>
+        <v>-110300</v>
       </c>
       <c r="F33" s="3">
-        <v>-483300</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+        <v>-200800</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-480100</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1359,9 +1431,12 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1386,23 +1461,26 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-111000</v>
+        <v>92600</v>
       </c>
       <c r="E35" s="3">
-        <v>-202100</v>
+        <v>-110300</v>
       </c>
       <c r="F35" s="3">
-        <v>-483300</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+        <v>-200800</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-480100</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1413,29 +1491,32 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1445,9 +1526,12 @@
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1459,8 +1543,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1472,22 +1557,23 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>542900</v>
+        <v>824100</v>
       </c>
       <c r="E41" s="3">
-        <v>956200</v>
+        <v>539300</v>
       </c>
       <c r="F41" s="3">
-        <v>521700</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>949900</v>
+      </c>
+      <c r="G41" s="3">
+        <v>518300</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1498,23 +1584,26 @@
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>107000</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
-        <v>34700</v>
+        <v>106300</v>
       </c>
       <c r="F42" s="3">
-        <v>85600</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+        <v>34500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>85100</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1525,23 +1614,26 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>81600</v>
+        <v>85900</v>
       </c>
       <c r="E43" s="3">
-        <v>119900</v>
+        <v>81100</v>
       </c>
       <c r="F43" s="3">
-        <v>79500</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>119100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>79000</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1552,23 +1644,26 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>32200</v>
+        <v>38000</v>
       </c>
       <c r="E44" s="3">
-        <v>27000</v>
+        <v>31900</v>
       </c>
       <c r="F44" s="3">
-        <v>25900</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>26900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>25700</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1579,23 +1674,26 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>47000</v>
+        <v>362100</v>
       </c>
       <c r="E45" s="3">
-        <v>41900</v>
+        <v>46700</v>
       </c>
       <c r="F45" s="3">
-        <v>133600</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>41600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>132800</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1606,23 +1704,26 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>810700</v>
+        <v>1310000</v>
       </c>
       <c r="E46" s="3">
-        <v>1179700</v>
+        <v>805400</v>
       </c>
       <c r="F46" s="3">
-        <v>846400</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>1172000</v>
+      </c>
+      <c r="G46" s="3">
+        <v>840900</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1633,23 +1734,26 @@
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>554200</v>
+        <v>513700</v>
       </c>
       <c r="E47" s="3">
-        <v>415000</v>
+        <v>550500</v>
       </c>
       <c r="F47" s="3">
-        <v>278400</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+        <v>412300</v>
+      </c>
+      <c r="G47" s="3">
+        <v>276600</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1660,23 +1764,26 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3862400</v>
+        <v>3433400</v>
       </c>
       <c r="E48" s="3">
-        <v>3991100</v>
+        <v>3837100</v>
       </c>
       <c r="F48" s="3">
-        <v>3994000</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>3964900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>3967800</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1687,23 +1794,26 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>871800</v>
+        <v>902100</v>
       </c>
       <c r="E49" s="3">
-        <v>893100</v>
+        <v>866100</v>
       </c>
       <c r="F49" s="3">
-        <v>906800</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+        <v>887300</v>
+      </c>
+      <c r="G49" s="3">
+        <v>900900</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1714,9 +1824,12 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1741,9 +1854,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1768,23 +1884,26 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13400</v>
+        <v>16100</v>
       </c>
       <c r="E52" s="3">
-        <v>13400</v>
+        <v>13300</v>
       </c>
       <c r="F52" s="3">
         <v>13300</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>13200</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1795,9 +1914,12 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1822,23 +1944,26 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6112400</v>
+        <v>6175200</v>
       </c>
       <c r="E54" s="3">
-        <v>6492300</v>
+        <v>6072300</v>
       </c>
       <c r="F54" s="3">
-        <v>6039000</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>6449700</v>
+      </c>
+      <c r="G54" s="3">
+        <v>5999400</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1849,9 +1974,12 @@
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1863,8 +1991,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1876,22 +2005,23 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>111700</v>
+        <v>98700</v>
       </c>
       <c r="E57" s="3">
-        <v>102200</v>
+        <v>111000</v>
       </c>
       <c r="F57" s="3">
-        <v>97000</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>101500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>96400</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1902,23 +2032,26 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>207900</v>
+        <v>49900</v>
       </c>
       <c r="E58" s="3">
-        <v>104500</v>
+        <v>206500</v>
       </c>
       <c r="F58" s="3">
-        <v>98900</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>103900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>98300</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1929,23 +2062,26 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>480600</v>
+        <v>518500</v>
       </c>
       <c r="E59" s="3">
-        <v>443500</v>
+        <v>477500</v>
       </c>
       <c r="F59" s="3">
-        <v>439700</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>440600</v>
+      </c>
+      <c r="G59" s="3">
+        <v>436900</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1956,23 +2092,26 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800200</v>
+        <v>667100</v>
       </c>
       <c r="E60" s="3">
-        <v>650300</v>
+        <v>795000</v>
       </c>
       <c r="F60" s="3">
-        <v>635700</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>646000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>631500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1983,23 +2122,26 @@
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2546100</v>
+        <v>2707600</v>
       </c>
       <c r="E61" s="3">
-        <v>2838700</v>
+        <v>2529400</v>
       </c>
       <c r="F61" s="3">
-        <v>2086900</v>
+        <v>2820100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>2073200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2010,24 +2152,27 @@
       <c r="J61" s="3">
         <v>0</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>252900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>217900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>172900</v>
+      </c>
+      <c r="G62" s="3">
         <v>219300</v>
       </c>
-      <c r="E62" s="3">
-        <v>174000</v>
-      </c>
-      <c r="F62" s="3">
-        <v>220700</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2037,9 +2182,12 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2064,9 +2212,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2091,9 +2242,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2118,23 +2272,26 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3414800</v>
+        <v>3454600</v>
       </c>
       <c r="E66" s="3">
-        <v>3549600</v>
+        <v>3392400</v>
       </c>
       <c r="F66" s="3">
-        <v>2855500</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>3526300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2836800</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2145,9 +2302,12 @@
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2159,8 +2319,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2185,9 +2346,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2212,9 +2376,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2239,9 +2406,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2266,23 +2436,26 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2124400</v>
+        <v>2021800</v>
       </c>
       <c r="E72" s="3">
-        <v>2417400</v>
+        <v>2110400</v>
       </c>
       <c r="F72" s="3">
-        <v>2717600</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>2401500</v>
+      </c>
+      <c r="G72" s="3">
+        <v>2699700</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2293,9 +2466,12 @@
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2320,9 +2496,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2347,9 +2526,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2374,23 +2556,26 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2697600</v>
+        <v>2720600</v>
       </c>
       <c r="E76" s="3">
-        <v>2942700</v>
+        <v>2679900</v>
       </c>
       <c r="F76" s="3">
-        <v>3183500</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>2923400</v>
+      </c>
+      <c r="G76" s="3">
+        <v>3162600</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2401,9 +2586,12 @@
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2428,29 +2616,32 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2460,23 +2651,26 @@
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-111000</v>
+        <v>92600</v>
       </c>
       <c r="E81" s="3">
-        <v>-202100</v>
+        <v>-110300</v>
       </c>
       <c r="F81" s="3">
-        <v>-483300</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+        <v>-200800</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-480100</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2487,9 +2681,12 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2501,22 +2698,23 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>264500</v>
+        <v>263200</v>
       </c>
       <c r="E83" s="3">
-        <v>236200</v>
+        <v>262700</v>
       </c>
       <c r="F83" s="3">
-        <v>238800</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+        <v>234600</v>
+      </c>
+      <c r="G83" s="3">
+        <v>237300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2527,9 +2725,12 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2554,9 +2755,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2581,9 +2785,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,9 +2815,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2635,9 +2845,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2662,23 +2875,26 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>504500</v>
+        <v>492500</v>
       </c>
       <c r="E89" s="3">
-        <v>100600</v>
+        <v>501100</v>
       </c>
       <c r="F89" s="3">
-        <v>-102700</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>99900</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-102100</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2689,9 +2905,12 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2703,22 +2922,23 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-139400</v>
+        <v>-147600</v>
       </c>
       <c r="E91" s="3">
-        <v>-184600</v>
+        <v>-138500</v>
       </c>
       <c r="F91" s="3">
-        <v>-228500</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-183400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-227000</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2729,9 +2949,12 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2756,9 +2979,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2783,23 +3009,26 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-242000</v>
+        <v>41200</v>
       </c>
       <c r="E94" s="3">
-        <v>-128200</v>
+        <v>-240400</v>
       </c>
       <c r="F94" s="3">
-        <v>-273500</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-127400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-271700</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2810,9 +3039,12 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2824,22 +3056,23 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-181200</v>
+        <v>-180300</v>
       </c>
       <c r="E96" s="3">
-        <v>-102500</v>
+        <v>-180000</v>
       </c>
       <c r="F96" s="3">
-        <v>-241200</v>
+        <v>-101900</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-239700</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2850,9 +3083,12 @@
       <c r="J96" s="3">
         <v>0</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -2877,9 +3113,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -2904,9 +3143,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -2931,23 +3173,26 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-611100</v>
+        <v>-376700</v>
       </c>
       <c r="E100" s="3">
-        <v>486500</v>
+        <v>-607100</v>
       </c>
       <c r="F100" s="3">
-        <v>-479400</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>483300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-476300</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2958,23 +3203,26 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E101" s="3">
         <v>7600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8300</v>
       </c>
-      <c r="F101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>-3300</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -2985,23 +3233,26 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-341000</v>
+        <v>178400</v>
       </c>
       <c r="E102" s="3">
-        <v>467100</v>
+        <v>-338800</v>
       </c>
       <c r="F102" s="3">
-        <v>-859000</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>464100</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-853300</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3012,7 +3263,10 @@
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
@@ -712,16 +712,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2161100</v>
+        <v>2370800</v>
       </c>
       <c r="E8" s="3">
-        <v>1824600</v>
+        <v>2001700</v>
       </c>
       <c r="F8" s="3">
-        <v>881600</v>
+        <v>967100</v>
       </c>
       <c r="G8" s="3">
-        <v>960500</v>
+        <v>1053700</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -742,16 +742,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1617300</v>
+        <v>1774200</v>
       </c>
       <c r="E9" s="3">
-        <v>1401300</v>
+        <v>1537200</v>
       </c>
       <c r="F9" s="3">
-        <v>848600</v>
+        <v>931000</v>
       </c>
       <c r="G9" s="3">
-        <v>981900</v>
+        <v>1077200</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -772,16 +772,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>543800</v>
+        <v>596500</v>
       </c>
       <c r="E10" s="3">
-        <v>423400</v>
+        <v>464400</v>
       </c>
       <c r="F10" s="3">
-        <v>33000</v>
+        <v>36200</v>
       </c>
       <c r="G10" s="3">
-        <v>-21400</v>
+        <v>-23500</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -876,16 +876,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="E14" s="3">
-        <v>77400</v>
+        <v>84900</v>
       </c>
       <c r="F14" s="3">
-        <v>48500</v>
+        <v>53200</v>
       </c>
       <c r="G14" s="3">
-        <v>125300</v>
+        <v>137400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -947,16 +947,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1836700</v>
+        <v>2014900</v>
       </c>
       <c r="E17" s="3">
-        <v>1738100</v>
+        <v>1906800</v>
       </c>
       <c r="F17" s="3">
-        <v>1005100</v>
+        <v>1102600</v>
       </c>
       <c r="G17" s="3">
-        <v>1283000</v>
+        <v>1407500</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -977,16 +977,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>324400</v>
+        <v>355900</v>
       </c>
       <c r="E18" s="3">
-        <v>86500</v>
+        <v>94900</v>
       </c>
       <c r="F18" s="3">
-        <v>-123500</v>
+        <v>-135400</v>
       </c>
       <c r="G18" s="3">
-        <v>-322500</v>
+        <v>-353800</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1021,16 +1021,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-54300</v>
+        <v>-59500</v>
       </c>
       <c r="E20" s="3">
-        <v>-48200</v>
+        <v>-52800</v>
       </c>
       <c r="F20" s="3">
-        <v>-51700</v>
+        <v>-56700</v>
       </c>
       <c r="G20" s="3">
-        <v>-65100</v>
+        <v>-71400</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1051,16 +1051,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>533300</v>
+        <v>582800</v>
       </c>
       <c r="E21" s="3">
-        <v>301000</v>
+        <v>327900</v>
       </c>
       <c r="F21" s="3">
-        <v>59400</v>
+        <v>63200</v>
       </c>
       <c r="G21" s="3">
-        <v>-150400</v>
+        <v>-167000</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1081,16 +1081,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>127100</v>
+        <v>139500</v>
       </c>
       <c r="E22" s="3">
-        <v>110900</v>
+        <v>121700</v>
       </c>
       <c r="F22" s="3">
-        <v>68300</v>
+        <v>74900</v>
       </c>
       <c r="G22" s="3">
-        <v>65800</v>
+        <v>72200</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1111,16 +1111,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>143000</v>
+        <v>156900</v>
       </c>
       <c r="E23" s="3">
-        <v>-72600</v>
+        <v>-79600</v>
       </c>
       <c r="F23" s="3">
-        <v>-243400</v>
+        <v>-267000</v>
       </c>
       <c r="G23" s="3">
-        <v>-453300</v>
+        <v>-497300</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1141,16 +1141,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>66400</v>
+        <v>72900</v>
       </c>
       <c r="E24" s="3">
-        <v>69000</v>
+        <v>75700</v>
       </c>
       <c r="F24" s="3">
-        <v>-20500</v>
+        <v>-22500</v>
       </c>
       <c r="G24" s="3">
-        <v>47500</v>
+        <v>52100</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1201,16 +1201,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>76500</v>
+        <v>84000</v>
       </c>
       <c r="E26" s="3">
-        <v>-141500</v>
+        <v>-155300</v>
       </c>
       <c r="F26" s="3">
-        <v>-222900</v>
+        <v>-244500</v>
       </c>
       <c r="G26" s="3">
-        <v>-500900</v>
+        <v>-549500</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1231,16 +1231,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>92600</v>
+        <v>101600</v>
       </c>
       <c r="E27" s="3">
-        <v>-110300</v>
+        <v>-121000</v>
       </c>
       <c r="F27" s="3">
-        <v>-200800</v>
+        <v>-220300</v>
       </c>
       <c r="G27" s="3">
-        <v>-480100</v>
+        <v>-526700</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1381,16 +1381,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>54300</v>
+        <v>59500</v>
       </c>
       <c r="E32" s="3">
-        <v>48200</v>
+        <v>52800</v>
       </c>
       <c r="F32" s="3">
-        <v>51700</v>
+        <v>56700</v>
       </c>
       <c r="G32" s="3">
-        <v>65100</v>
+        <v>71400</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1411,16 +1411,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>92600</v>
+        <v>101600</v>
       </c>
       <c r="E33" s="3">
-        <v>-110300</v>
+        <v>-121000</v>
       </c>
       <c r="F33" s="3">
-        <v>-200800</v>
+        <v>-220300</v>
       </c>
       <c r="G33" s="3">
-        <v>-480100</v>
+        <v>-526700</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1471,16 +1471,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>92600</v>
+        <v>101600</v>
       </c>
       <c r="E35" s="3">
-        <v>-110300</v>
+        <v>-121000</v>
       </c>
       <c r="F35" s="3">
-        <v>-200800</v>
+        <v>-220300</v>
       </c>
       <c r="G35" s="3">
-        <v>-480100</v>
+        <v>-526700</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1564,16 +1564,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>824100</v>
+        <v>904000</v>
       </c>
       <c r="E41" s="3">
-        <v>539300</v>
+        <v>591700</v>
       </c>
       <c r="F41" s="3">
-        <v>949900</v>
+        <v>1042100</v>
       </c>
       <c r="G41" s="3">
-        <v>518300</v>
+        <v>568600</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1597,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="E42" s="3">
-        <v>106300</v>
+        <v>116600</v>
       </c>
       <c r="F42" s="3">
-        <v>34500</v>
+        <v>37800</v>
       </c>
       <c r="G42" s="3">
-        <v>85100</v>
+        <v>93300</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1624,16 +1624,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>85900</v>
+        <v>94300</v>
       </c>
       <c r="E43" s="3">
-        <v>81100</v>
+        <v>89000</v>
       </c>
       <c r="F43" s="3">
-        <v>119100</v>
+        <v>130600</v>
       </c>
       <c r="G43" s="3">
-        <v>79000</v>
+        <v>86700</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1654,16 +1654,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>38000</v>
+        <v>41700</v>
       </c>
       <c r="E44" s="3">
-        <v>31900</v>
+        <v>35000</v>
       </c>
       <c r="F44" s="3">
-        <v>26900</v>
+        <v>29500</v>
       </c>
       <c r="G44" s="3">
-        <v>25700</v>
+        <v>28200</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1684,16 +1684,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>362100</v>
+        <v>397200</v>
       </c>
       <c r="E45" s="3">
-        <v>46700</v>
+        <v>51200</v>
       </c>
       <c r="F45" s="3">
-        <v>41600</v>
+        <v>45700</v>
       </c>
       <c r="G45" s="3">
-        <v>132800</v>
+        <v>145700</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1714,16 +1714,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1310000</v>
+        <v>1437200</v>
       </c>
       <c r="E46" s="3">
-        <v>805400</v>
+        <v>883500</v>
       </c>
       <c r="F46" s="3">
-        <v>1172000</v>
+        <v>1285700</v>
       </c>
       <c r="G46" s="3">
-        <v>840900</v>
+        <v>922400</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1744,16 +1744,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>513700</v>
+        <v>563600</v>
       </c>
       <c r="E47" s="3">
-        <v>550500</v>
+        <v>604000</v>
       </c>
       <c r="F47" s="3">
-        <v>412300</v>
+        <v>452300</v>
       </c>
       <c r="G47" s="3">
-        <v>276600</v>
+        <v>303400</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1774,16 +1774,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3433400</v>
+        <v>3766500</v>
       </c>
       <c r="E48" s="3">
-        <v>3837100</v>
+        <v>4209400</v>
       </c>
       <c r="F48" s="3">
-        <v>3964900</v>
+        <v>4349600</v>
       </c>
       <c r="G48" s="3">
-        <v>3967800</v>
+        <v>4352900</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1804,16 +1804,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>902100</v>
+        <v>989600</v>
       </c>
       <c r="E49" s="3">
-        <v>866100</v>
+        <v>950100</v>
       </c>
       <c r="F49" s="3">
-        <v>887300</v>
+        <v>973400</v>
       </c>
       <c r="G49" s="3">
-        <v>900900</v>
+        <v>988300</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1894,16 +1894,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16100</v>
+        <v>17600</v>
       </c>
       <c r="E52" s="3">
-        <v>13300</v>
+        <v>14600</v>
       </c>
       <c r="F52" s="3">
-        <v>13300</v>
+        <v>14600</v>
       </c>
       <c r="G52" s="3">
-        <v>13200</v>
+        <v>14500</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1954,16 +1954,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6175200</v>
+        <v>6774400</v>
       </c>
       <c r="E54" s="3">
-        <v>6072300</v>
+        <v>6661600</v>
       </c>
       <c r="F54" s="3">
-        <v>6449700</v>
+        <v>7075600</v>
       </c>
       <c r="G54" s="3">
-        <v>5999400</v>
+        <v>6581600</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2012,16 +2012,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>98700</v>
+        <v>108300</v>
       </c>
       <c r="E57" s="3">
-        <v>111000</v>
+        <v>121800</v>
       </c>
       <c r="F57" s="3">
-        <v>101500</v>
+        <v>111400</v>
       </c>
       <c r="G57" s="3">
-        <v>96400</v>
+        <v>105700</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2042,16 +2042,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>49900</v>
+        <v>54700</v>
       </c>
       <c r="E58" s="3">
-        <v>206500</v>
+        <v>226600</v>
       </c>
       <c r="F58" s="3">
-        <v>103900</v>
+        <v>113900</v>
       </c>
       <c r="G58" s="3">
-        <v>98300</v>
+        <v>107800</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2072,16 +2072,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>518500</v>
+        <v>568900</v>
       </c>
       <c r="E59" s="3">
-        <v>477500</v>
+        <v>523800</v>
       </c>
       <c r="F59" s="3">
-        <v>440600</v>
+        <v>483400</v>
       </c>
       <c r="G59" s="3">
-        <v>436900</v>
+        <v>479300</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2102,16 +2102,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>667100</v>
+        <v>731800</v>
       </c>
       <c r="E60" s="3">
-        <v>795000</v>
+        <v>872100</v>
       </c>
       <c r="F60" s="3">
-        <v>646000</v>
+        <v>708700</v>
       </c>
       <c r="G60" s="3">
-        <v>631500</v>
+        <v>692800</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2132,16 +2132,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2707600</v>
+        <v>2970300</v>
       </c>
       <c r="E61" s="3">
-        <v>2529400</v>
+        <v>2774900</v>
       </c>
       <c r="F61" s="3">
-        <v>2820100</v>
+        <v>3093700</v>
       </c>
       <c r="G61" s="3">
-        <v>2073200</v>
+        <v>2274300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2162,16 +2162,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>252900</v>
+        <v>277400</v>
       </c>
       <c r="E62" s="3">
-        <v>217900</v>
+        <v>239000</v>
       </c>
       <c r="F62" s="3">
-        <v>172900</v>
+        <v>189600</v>
       </c>
       <c r="G62" s="3">
-        <v>219300</v>
+        <v>240500</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2282,16 +2282,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3454600</v>
+        <v>3789800</v>
       </c>
       <c r="E66" s="3">
-        <v>3392400</v>
+        <v>3721600</v>
       </c>
       <c r="F66" s="3">
-        <v>3526300</v>
+        <v>3868500</v>
       </c>
       <c r="G66" s="3">
-        <v>2836800</v>
+        <v>3112000</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2446,16 +2446,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2021800</v>
+        <v>2218000</v>
       </c>
       <c r="E72" s="3">
-        <v>2110400</v>
+        <v>2315200</v>
       </c>
       <c r="F72" s="3">
-        <v>2401500</v>
+        <v>2634500</v>
       </c>
       <c r="G72" s="3">
-        <v>2699700</v>
+        <v>2961700</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2566,16 +2566,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2720600</v>
+        <v>2984600</v>
       </c>
       <c r="E76" s="3">
-        <v>2679900</v>
+        <v>2940000</v>
       </c>
       <c r="F76" s="3">
-        <v>2923400</v>
+        <v>3207100</v>
       </c>
       <c r="G76" s="3">
-        <v>3162600</v>
+        <v>3469500</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2661,16 +2661,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>92600</v>
+        <v>101600</v>
       </c>
       <c r="E81" s="3">
-        <v>-110300</v>
+        <v>-121000</v>
       </c>
       <c r="F81" s="3">
-        <v>-200800</v>
+        <v>-220300</v>
       </c>
       <c r="G81" s="3">
-        <v>-480100</v>
+        <v>-526700</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2705,16 +2705,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>263200</v>
+        <v>288800</v>
       </c>
       <c r="E83" s="3">
-        <v>262700</v>
+        <v>288200</v>
       </c>
       <c r="F83" s="3">
-        <v>234600</v>
+        <v>257400</v>
       </c>
       <c r="G83" s="3">
-        <v>237300</v>
+        <v>260300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2885,16 +2885,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>492500</v>
+        <v>540200</v>
       </c>
       <c r="E89" s="3">
-        <v>501100</v>
+        <v>549800</v>
       </c>
       <c r="F89" s="3">
-        <v>99900</v>
+        <v>109600</v>
       </c>
       <c r="G89" s="3">
-        <v>-102100</v>
+        <v>-112000</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2929,16 +2929,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-147600</v>
+        <v>-161900</v>
       </c>
       <c r="E91" s="3">
-        <v>-138500</v>
+        <v>-152000</v>
       </c>
       <c r="F91" s="3">
-        <v>-183400</v>
+        <v>-201200</v>
       </c>
       <c r="G91" s="3">
-        <v>-227000</v>
+        <v>-249100</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3019,16 +3019,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>41200</v>
+        <v>45200</v>
       </c>
       <c r="E94" s="3">
-        <v>-240400</v>
+        <v>-263700</v>
       </c>
       <c r="F94" s="3">
-        <v>-127400</v>
+        <v>-139800</v>
       </c>
       <c r="G94" s="3">
-        <v>-271700</v>
+        <v>-298000</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3063,16 +3063,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-180300</v>
+        <v>-197800</v>
       </c>
       <c r="E96" s="3">
-        <v>-180000</v>
+        <v>-197500</v>
       </c>
       <c r="F96" s="3">
-        <v>-101900</v>
+        <v>-111800</v>
       </c>
       <c r="G96" s="3">
-        <v>-239700</v>
+        <v>-262900</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -3183,16 +3183,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-376700</v>
+        <v>-413200</v>
       </c>
       <c r="E100" s="3">
-        <v>-607100</v>
+        <v>-666000</v>
       </c>
       <c r="F100" s="3">
-        <v>483300</v>
+        <v>530200</v>
       </c>
       <c r="G100" s="3">
-        <v>-476300</v>
+        <v>-522500</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3213,16 +3213,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>21400</v>
+        <v>23500</v>
       </c>
       <c r="E101" s="3">
-        <v>7600</v>
+        <v>8300</v>
       </c>
       <c r="F101" s="3">
-        <v>8300</v>
+        <v>9100</v>
       </c>
       <c r="G101" s="3">
-        <v>-3300</v>
+        <v>-3700</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3243,16 +3243,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>178400</v>
+        <v>195700</v>
       </c>
       <c r="E102" s="3">
-        <v>-338800</v>
+        <v>-371600</v>
       </c>
       <c r="F102" s="3">
-        <v>464100</v>
+        <v>509100</v>
       </c>
       <c r="G102" s="3">
-        <v>-853300</v>
+        <v>-936100</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>GMALY</t>
   </si>
@@ -662,8 +662,8 @@
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,14 +693,14 @@
       <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -712,25 +712,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2370800</v>
+        <v>2221100</v>
       </c>
       <c r="E8" s="3">
-        <v>2001700</v>
+        <v>1964200</v>
       </c>
       <c r="F8" s="3">
-        <v>967100</v>
+        <v>997600</v>
       </c>
       <c r="G8" s="3">
-        <v>1053700</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>1126900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2541400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2400600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2294400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -742,25 +742,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1774200</v>
+        <v>1662300</v>
       </c>
       <c r="E9" s="3">
-        <v>1537200</v>
+        <v>1508400</v>
       </c>
       <c r="F9" s="3">
-        <v>931000</v>
+        <v>960400</v>
       </c>
       <c r="G9" s="3">
-        <v>1077200</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>1152000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1932200</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1756800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1754700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -772,25 +772,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>596500</v>
+        <v>558900</v>
       </c>
       <c r="E10" s="3">
-        <v>464400</v>
+        <v>455700</v>
       </c>
       <c r="F10" s="3">
-        <v>36200</v>
+        <v>37300</v>
       </c>
       <c r="G10" s="3">
-        <v>-23500</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>-25100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>609200</v>
+      </c>
+      <c r="I10" s="3">
+        <v>643700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>539700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -876,25 +876,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>6900</v>
+        <v>-35900</v>
       </c>
       <c r="E14" s="3">
-        <v>84900</v>
+        <v>94200</v>
       </c>
       <c r="F14" s="3">
-        <v>53200</v>
+        <v>10800</v>
       </c>
       <c r="G14" s="3">
-        <v>137400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>148800</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>469700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>14000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -906,25 +906,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>250600</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>264500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>243000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>253400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>237300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>229100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>229100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -947,25 +947,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2014900</v>
+        <v>1909500</v>
       </c>
       <c r="E17" s="3">
-        <v>1906800</v>
+        <v>1726300</v>
       </c>
       <c r="F17" s="3">
-        <v>1102600</v>
+        <v>1128100</v>
       </c>
       <c r="G17" s="3">
-        <v>1407500</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>1383700</v>
+      </c>
+      <c r="H17" s="3">
+        <v>2189500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1973700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1991300</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -977,25 +977,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>355900</v>
+        <v>311600</v>
       </c>
       <c r="E18" s="3">
-        <v>94900</v>
+        <v>237800</v>
       </c>
       <c r="F18" s="3">
-        <v>-135400</v>
+        <v>-130400</v>
       </c>
       <c r="G18" s="3">
-        <v>-353800</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>-256800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>351800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>426900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>303100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1021,25 +1021,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-59500</v>
+        <v>94600</v>
       </c>
       <c r="E20" s="3">
-        <v>-52800</v>
+        <v>111400</v>
       </c>
       <c r="F20" s="3">
-        <v>-56700</v>
+        <v>64300</v>
       </c>
       <c r="G20" s="3">
-        <v>-71400</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>71300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-58800</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1051,25 +1051,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>582800</v>
+        <v>467600</v>
       </c>
       <c r="E21" s="3">
-        <v>327900</v>
+        <v>390900</v>
       </c>
       <c r="F21" s="3">
-        <v>63200</v>
+        <v>48200</v>
       </c>
       <c r="G21" s="3">
-        <v>-167000</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-74700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>577900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>657400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>591100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1081,25 +1081,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>139500</v>
+        <v>130700</v>
       </c>
       <c r="E22" s="3">
-        <v>121700</v>
+        <v>119400</v>
       </c>
       <c r="F22" s="3">
-        <v>74900</v>
+        <v>77300</v>
       </c>
       <c r="G22" s="3">
-        <v>72200</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>77200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>76400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>36200</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1111,25 +1111,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>156900</v>
+        <v>147000</v>
       </c>
       <c r="E23" s="3">
-        <v>-79600</v>
+        <v>-78100</v>
       </c>
       <c r="F23" s="3">
-        <v>-267000</v>
+        <v>-275500</v>
       </c>
       <c r="G23" s="3">
-        <v>-497300</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>-531900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>363700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>324600</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>72900</v>
+        <v>68300</v>
       </c>
       <c r="E24" s="3">
-        <v>75700</v>
+        <v>74200</v>
       </c>
       <c r="F24" s="3">
-        <v>-22500</v>
+        <v>-23200</v>
       </c>
       <c r="G24" s="3">
-        <v>52100</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>55700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>38400</v>
+      </c>
+      <c r="I24" s="3">
+        <v>19900</v>
+      </c>
+      <c r="J24" s="3">
+        <v>60800</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1201,25 +1201,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>84000</v>
+        <v>78700</v>
       </c>
       <c r="E26" s="3">
-        <v>-155300</v>
+        <v>-152400</v>
       </c>
       <c r="F26" s="3">
-        <v>-244500</v>
+        <v>-252300</v>
       </c>
       <c r="G26" s="3">
-        <v>-549500</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>-587600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>325300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>263800</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1231,25 +1231,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>101600</v>
+        <v>95200</v>
       </c>
       <c r="E27" s="3">
-        <v>-121000</v>
+        <v>-118700</v>
       </c>
       <c r="F27" s="3">
-        <v>-220300</v>
+        <v>-227200</v>
       </c>
       <c r="G27" s="3">
-        <v>-526700</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>-563300</v>
+      </c>
+      <c r="H27" s="3">
+        <v>340700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J27" s="3">
+        <v>285600</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1381,25 +1381,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>59500</v>
+        <v>-94600</v>
       </c>
       <c r="E32" s="3">
-        <v>52800</v>
+        <v>-111400</v>
       </c>
       <c r="F32" s="3">
-        <v>56700</v>
+        <v>-64300</v>
       </c>
       <c r="G32" s="3">
-        <v>71400</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>-71300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>58800</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1411,25 +1411,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>101600</v>
+        <v>95200</v>
       </c>
       <c r="E33" s="3">
-        <v>-121000</v>
+        <v>-118700</v>
       </c>
       <c r="F33" s="3">
-        <v>-220300</v>
+        <v>-227200</v>
       </c>
       <c r="G33" s="3">
-        <v>-526700</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>-563300</v>
+      </c>
+      <c r="H33" s="3">
+        <v>340700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J33" s="3">
+        <v>285600</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1471,25 +1471,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>101600</v>
+        <v>95200</v>
       </c>
       <c r="E35" s="3">
-        <v>-121000</v>
+        <v>-118700</v>
       </c>
       <c r="F35" s="3">
-        <v>-220300</v>
+        <v>-227200</v>
       </c>
       <c r="G35" s="3">
-        <v>-526700</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>-563300</v>
+      </c>
+      <c r="H35" s="3">
+        <v>340700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J35" s="3">
+        <v>285600</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1517,14 +1517,14 @@
       <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1564,25 +1564,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>904000</v>
+        <v>846800</v>
       </c>
       <c r="E41" s="3">
-        <v>591700</v>
+        <v>694900</v>
       </c>
       <c r="F41" s="3">
-        <v>1042100</v>
+        <v>1113900</v>
       </c>
       <c r="G41" s="3">
-        <v>568600</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>610400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1581500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1934400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1474600</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1593,26 +1593,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>11400</v>
       </c>
       <c r="E42" s="3">
-        <v>116600</v>
+        <v>8700</v>
       </c>
       <c r="F42" s="3">
-        <v>37800</v>
+        <v>7400</v>
       </c>
       <c r="G42" s="3">
-        <v>93300</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>98400</v>
+      </c>
+      <c r="H42" s="3">
+        <v>196600</v>
+      </c>
+      <c r="I42" s="3">
+        <v>105500</v>
+      </c>
+      <c r="J42" s="3">
+        <v>38500</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -1624,25 +1624,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>94300</v>
+        <v>88300</v>
       </c>
       <c r="E43" s="3">
-        <v>89000</v>
+        <v>87300</v>
       </c>
       <c r="F43" s="3">
-        <v>130600</v>
+        <v>134800</v>
       </c>
       <c r="G43" s="3">
-        <v>86700</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>92700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>109000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>105700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>107900</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1654,25 +1654,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>41700</v>
+        <v>39000</v>
       </c>
       <c r="E44" s="3">
-        <v>35000</v>
+        <v>34400</v>
       </c>
       <c r="F44" s="3">
-        <v>29500</v>
+        <v>30400</v>
       </c>
       <c r="G44" s="3">
-        <v>28200</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>30200</v>
+      </c>
+      <c r="H44" s="3">
+        <v>30100</v>
+      </c>
+      <c r="I44" s="3">
+        <v>26200</v>
+      </c>
+      <c r="J44" s="3">
+        <v>27400</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1684,25 +1684,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>397200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>51200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>45700</v>
+        <v>306700</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>145700</v>
+        <v>101200</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>14400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>16200</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1714,25 +1714,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1437200</v>
+        <v>1346400</v>
       </c>
       <c r="E46" s="3">
-        <v>883500</v>
+        <v>867000</v>
       </c>
       <c r="F46" s="3">
-        <v>1285700</v>
+        <v>1326200</v>
       </c>
       <c r="G46" s="3">
-        <v>922400</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>986500</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1968900</v>
+      </c>
+      <c r="I46" s="3">
+        <v>2258200</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1735900</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1744,25 +1744,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>563600</v>
+        <v>457500</v>
       </c>
       <c r="E47" s="3">
-        <v>604000</v>
+        <v>523300</v>
       </c>
       <c r="F47" s="3">
-        <v>452300</v>
+        <v>461600</v>
       </c>
       <c r="G47" s="3">
-        <v>303400</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>306700</v>
+      </c>
+      <c r="H47" s="3">
+        <v>212000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>64600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>72500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1774,25 +1774,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3766500</v>
+        <v>3291900</v>
       </c>
       <c r="E48" s="3">
-        <v>4209400</v>
+        <v>3654900</v>
       </c>
       <c r="F48" s="3">
-        <v>4349600</v>
+        <v>4003000</v>
       </c>
       <c r="G48" s="3">
-        <v>4352900</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>4178900</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4271800</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3588700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3402300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -1804,25 +1804,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>989600</v>
+        <v>927100</v>
       </c>
       <c r="E49" s="3">
-        <v>950100</v>
+        <v>932300</v>
       </c>
       <c r="F49" s="3">
-        <v>973400</v>
+        <v>1004100</v>
       </c>
       <c r="G49" s="3">
-        <v>988300</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>1057000</v>
+      </c>
+      <c r="H49" s="3">
+        <v>1092300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1094700</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1144600</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -1894,25 +1894,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17600</v>
+        <v>243900</v>
       </c>
       <c r="E52" s="3">
-        <v>14600</v>
+        <v>483200</v>
       </c>
       <c r="F52" s="3">
-        <v>14600</v>
+        <v>491100</v>
       </c>
       <c r="G52" s="3">
-        <v>14500</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>496700</v>
+      </c>
+      <c r="H52" s="3">
+        <v>517800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>601100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>605300</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -1954,25 +1954,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>6774400</v>
+        <v>6346800</v>
       </c>
       <c r="E54" s="3">
-        <v>6661600</v>
+        <v>6536800</v>
       </c>
       <c r="F54" s="3">
-        <v>7075600</v>
+        <v>7298800</v>
       </c>
       <c r="G54" s="3">
-        <v>6581600</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>7038700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>8135000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>7669700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>7369600</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2012,25 +2012,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>108300</v>
+        <v>101400</v>
       </c>
       <c r="E57" s="3">
-        <v>121800</v>
+        <v>119500</v>
       </c>
       <c r="F57" s="3">
-        <v>111400</v>
+        <v>114900</v>
       </c>
       <c r="G57" s="3">
-        <v>105700</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>117200</v>
+      </c>
+      <c r="H57" s="3">
+        <v>150600</v>
+      </c>
+      <c r="I57" s="3">
+        <v>153400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>161100</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2042,25 +2042,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>54700</v>
+        <v>51300</v>
       </c>
       <c r="E58" s="3">
-        <v>226600</v>
+        <v>222300</v>
       </c>
       <c r="F58" s="3">
-        <v>113900</v>
+        <v>117800</v>
       </c>
       <c r="G58" s="3">
-        <v>107800</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>116400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>394800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>115500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>94300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2072,25 +2072,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>568900</v>
+        <v>168900</v>
       </c>
       <c r="E59" s="3">
-        <v>523800</v>
+        <v>182000</v>
       </c>
       <c r="F59" s="3">
-        <v>483400</v>
+        <v>221000</v>
       </c>
       <c r="G59" s="3">
-        <v>479300</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>195900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>254200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>220500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>208000</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2102,25 +2102,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>731800</v>
+        <v>685600</v>
       </c>
       <c r="E60" s="3">
-        <v>872100</v>
+        <v>855800</v>
       </c>
       <c r="F60" s="3">
-        <v>708700</v>
+        <v>731100</v>
       </c>
       <c r="G60" s="3">
-        <v>692800</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>740900</v>
+      </c>
+      <c r="H60" s="3">
+        <v>1154400</v>
+      </c>
+      <c r="I60" s="3">
+        <v>818100</v>
+      </c>
+      <c r="J60" s="3">
+        <v>800000</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2132,25 +2132,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2970300</v>
+        <v>2782800</v>
       </c>
       <c r="E61" s="3">
-        <v>2774900</v>
+        <v>2722900</v>
       </c>
       <c r="F61" s="3">
-        <v>3093700</v>
+        <v>3191300</v>
       </c>
       <c r="G61" s="3">
-        <v>2274300</v>
+        <v>2433000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2262700</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>2244600</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1620800</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2162,25 +2162,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>277400</v>
+        <v>900</v>
       </c>
       <c r="E62" s="3">
-        <v>239000</v>
+        <v>2600</v>
       </c>
       <c r="F62" s="3">
-        <v>189600</v>
+        <v>2200</v>
       </c>
       <c r="G62" s="3">
-        <v>240500</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>2900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>4400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2282,25 +2282,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3789800</v>
+        <v>3728400</v>
       </c>
       <c r="E66" s="3">
-        <v>3721600</v>
+        <v>3813200</v>
       </c>
       <c r="F66" s="3">
-        <v>3868500</v>
+        <v>4118000</v>
       </c>
       <c r="G66" s="3">
-        <v>3112000</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>3430500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>3697900</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3328400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>2665200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2446,25 +2446,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2218000</v>
+        <v>2096300</v>
       </c>
       <c r="E72" s="3">
-        <v>2315200</v>
+        <v>2291000</v>
       </c>
       <c r="F72" s="3">
-        <v>2634500</v>
+        <v>2737800</v>
       </c>
       <c r="G72" s="3">
-        <v>2961700</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>3188300</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3957600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>3838000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4173300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2566,25 +2566,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2984600</v>
+        <v>2796200</v>
       </c>
       <c r="E76" s="3">
-        <v>2940000</v>
+        <v>2884900</v>
       </c>
       <c r="F76" s="3">
-        <v>3207100</v>
+        <v>3308200</v>
       </c>
       <c r="G76" s="3">
-        <v>3469500</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>3710500</v>
+      </c>
+      <c r="H76" s="3">
+        <v>4517100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>4405900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4751900</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2642,14 +2642,14 @@
       <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2661,25 +2661,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>101600</v>
+        <v>95200</v>
       </c>
       <c r="E81" s="3">
-        <v>-121000</v>
+        <v>-118700</v>
       </c>
       <c r="F81" s="3">
-        <v>-220300</v>
+        <v>-227200</v>
       </c>
       <c r="G81" s="3">
-        <v>-526700</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>-563300</v>
+      </c>
+      <c r="H81" s="3">
+        <v>340700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J81" s="3">
+        <v>285600</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -2705,25 +2705,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>288800</v>
+        <v>245600</v>
       </c>
       <c r="E83" s="3">
-        <v>288200</v>
+        <v>257600</v>
       </c>
       <c r="F83" s="3">
-        <v>257400</v>
+        <v>239100</v>
       </c>
       <c r="G83" s="3">
-        <v>260300</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>250500</v>
+      </c>
+      <c r="H83" s="3">
+        <v>234100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>203000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>200900</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -2885,25 +2885,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>540200</v>
+        <v>506100</v>
       </c>
       <c r="E89" s="3">
-        <v>549800</v>
+        <v>539500</v>
       </c>
       <c r="F89" s="3">
-        <v>109600</v>
+        <v>113000</v>
       </c>
       <c r="G89" s="3">
-        <v>-112000</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>-119700</v>
+      </c>
+      <c r="H89" s="3">
+        <v>629400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>631200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>529900</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -2929,25 +2929,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-161900</v>
+        <v>-151700</v>
       </c>
       <c r="E91" s="3">
-        <v>-152000</v>
+        <v>-149100</v>
       </c>
       <c r="F91" s="3">
-        <v>-201200</v>
+        <v>-207600</v>
       </c>
       <c r="G91" s="3">
-        <v>-249100</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-266400</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-614900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-448200</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-653900</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3019,25 +3019,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>45200</v>
+        <v>42400</v>
       </c>
       <c r="E94" s="3">
-        <v>-263700</v>
+        <v>-258800</v>
       </c>
       <c r="F94" s="3">
-        <v>-139800</v>
+        <v>-144200</v>
       </c>
       <c r="G94" s="3">
-        <v>-298000</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-318700</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-640300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-440400</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-560800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3063,25 +3063,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-197800</v>
+        <v>185300</v>
       </c>
       <c r="E96" s="3">
-        <v>-197500</v>
+        <v>77600</v>
       </c>
       <c r="F96" s="3">
-        <v>-111800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-262900</v>
+        <v>154700</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>151900</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>150500</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>142000</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-413200</v>
+        <v>-387100</v>
       </c>
       <c r="E100" s="3">
-        <v>-666000</v>
+        <v>-653500</v>
       </c>
       <c r="F100" s="3">
-        <v>530200</v>
+        <v>546900</v>
       </c>
       <c r="G100" s="3">
-        <v>-522500</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-558800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-356900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>290000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>354600</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3213,25 +3213,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>23500</v>
+        <v>22000</v>
       </c>
       <c r="E101" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="F101" s="3">
-        <v>9100</v>
+        <v>9400</v>
       </c>
       <c r="G101" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-3900</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-43100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -3243,25 +3243,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>195700</v>
+        <v>183400</v>
       </c>
       <c r="E102" s="3">
-        <v>-371600</v>
+        <v>-364700</v>
       </c>
       <c r="F102" s="3">
-        <v>509100</v>
+        <v>525200</v>
       </c>
       <c r="G102" s="3">
-        <v>-936100</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-1001200</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-372000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>484400</v>
+      </c>
+      <c r="J102" s="3">
+        <v>280600</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GMALY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>GMALY</t>
   </si>
@@ -656,148 +656,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2440400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2221100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1964200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>997600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1126900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2541400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2400600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2294400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1870100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1662300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1508400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>960400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1152000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1932200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1756800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1754700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>570400</v>
+      </c>
+      <c r="E10" s="3">
         <v>558900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>455700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-25100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>609200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>643700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>539700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,8 +822,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,69 +885,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-35900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>94200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>148800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-51200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>469700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>277400</v>
+      </c>
+      <c r="E15" s="3">
         <v>250600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>264500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>243000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>253400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>237300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>229100</v>
       </c>
       <c r="J15" s="3">
         <v>229100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+        <v>229100</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,68 +966,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2117200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1909500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1726300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1128100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1383700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2189500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1973700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1991300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>323200</v>
+      </c>
+      <c r="E18" s="3">
         <v>311600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>237800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-130400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-256800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>351800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>426900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>303100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,158 +1047,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E20" s="3">
         <v>94600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>111400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>64300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>71300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-58800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>520500</v>
+      </c>
+      <c r="E21" s="3">
         <v>467600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>390900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>48200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-74700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>577900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>657400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>591100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E22" s="3">
         <v>130700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>119400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>77300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>77200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>76400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>50000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E23" s="3">
         <v>147000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-78100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-275500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-531900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>363700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>324600</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E24" s="3">
         <v>68300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>74200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-23200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>55700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>60800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,69 +1242,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E26" s="3">
         <v>78700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-152400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-252300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-587600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>325300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>263800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E27" s="3">
         <v>95200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-118700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-227200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-563300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>340700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>285600</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,69 +1440,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-94600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-111400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-64300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-71300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>58800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E33" s="3">
         <v>95200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-118700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-227200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-563300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>340700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>285600</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,74 +1539,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E35" s="3">
         <v>95200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-118700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-227200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-563300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>340700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>285600</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,278 +1643,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>791000</v>
+      </c>
+      <c r="E41" s="3">
         <v>846800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>694900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1113900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>610400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1581500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1934400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1474600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>11400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>98400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>196600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>105500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>38500</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E43" s="3">
         <v>88300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>87300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>134800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>92700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>105700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E44" s="3">
         <v>39000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>34400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>30200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>30100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>27400</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
         <v>306700</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>101200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>14400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>962700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1346400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>867000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1326200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>986500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1968900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2258200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1735900</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>588300</v>
+      </c>
+      <c r="E47" s="3">
         <v>457500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>523300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>461600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>306700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>212000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>64600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>72500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3288400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3291900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3654900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4003000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4178900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4271800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3588700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3402300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>894600</v>
+      </c>
+      <c r="E49" s="3">
         <v>927100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>932300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1004100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1057000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1092300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1094700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1144600</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,39 +2003,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>645700</v>
+      </c>
+      <c r="E52" s="3">
         <v>243900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>483200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>491100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>496700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>517800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>601100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>605300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,39 +2069,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6389100</v>
+      </c>
+      <c r="E54" s="3">
         <v>6346800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6536800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7298800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7038700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8135000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7669700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7369600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,188 +2135,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>654400</v>
+      </c>
+      <c r="E57" s="3">
         <v>101400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>119500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>114900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>117200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>150600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>153400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>161100</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E58" s="3">
         <v>51300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>222300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>117800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>116400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>394800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>115500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>94300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E59" s="3">
         <v>168900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>182000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>221000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>195900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>254200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>220500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>208000</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>747500</v>
+      </c>
+      <c r="E60" s="3">
         <v>685600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>855800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>731100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>740900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1154400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>818100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>800000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2900100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2782800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2722900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3191300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2433000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2262700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2244600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1620800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3800</v>
       </c>
       <c r="I62" s="3">
         <v>3800</v>
       </c>
       <c r="J62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K62" s="3">
         <v>4400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,39 +2429,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3920200</v>
+      </c>
+      <c r="E66" s="3">
         <v>3728400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3813200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4118000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3430500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3697900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3328400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2665200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,39 +2609,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2017600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2096300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2291000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2737800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3188300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3957600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3838000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4173300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,39 +2741,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2666200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2796200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2884900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3308200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3710500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4517100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4405900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4751900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,74 +2807,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E81" s="3">
         <v>95200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-118700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-227200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-563300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>340700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>285600</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,38 +2896,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>277400</v>
+      </c>
+      <c r="E83" s="3">
         <v>245600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>257600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>239100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>250500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>234100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>203000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,39 +3091,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>519500</v>
+      </c>
+      <c r="E89" s="3">
         <v>506100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>539500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>113000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-119700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>629400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>631200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>529900</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,38 +3142,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-126800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-151700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-149100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-207600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-266400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-614900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-448200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-653900</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,39 +3238,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-264500</v>
+      </c>
+      <c r="E94" s="3">
         <v>42400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-258800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-144200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-318700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-640300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-440400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-560800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,38 +3289,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>190100</v>
+      </c>
+      <c r="E96" s="3">
         <v>185300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>77600</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>154700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>151900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>150500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>142000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,97 +3418,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-322500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-387100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-653500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>546900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-558800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-356900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>290000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>354600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E101" s="3">
         <v>22000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-43100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-77900</v>
+      </c>
+      <c r="E102" s="3">
         <v>183400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-364700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>525200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1001200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-372000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>484400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>280600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
